--- a/store/Jun-2026/Mail Attachment/Non_BTC_Report_03-Jun-2026.xlsx
+++ b/store/Jun-2026/Mail Attachment/Non_BTC_Report_03-Jun-2026.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:Q23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -771,37 +771,37 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>WTI-20260603-3910504</t>
+          <t>WTI-20260603-3910573</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Self</t>
+          <t>Atul Sharma</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Citicorp Services India Pvt. Ltd. (CSIPL)</t>
+          <t>Serentica Renewables India Private Limited - CRD</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SAURABH AGRAWAL</t>
+          <t>MR. AK SINGH</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-06-04 05:45:00</t>
+          <t>2026-06-03 22:20:00</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>9552537476</t>
+          <t>9250004449</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>saurabh1.agrawal@citi.com</t>
+          <t>manpreet.kaur@serentica.in</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-06-03 11:33:12.187000</t>
+          <t>2026-06-03 12:18:25.863000</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -826,27 +826,27 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Pune Hub 1</t>
+          <t>Noida</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Outstation</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>SA56291</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>SA56291</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>SA56291</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -854,42 +854,42 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>WTI-20260603-3910536</t>
+          <t>WTI-20260603-3910504</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Travel Desk</t>
+          <t>Self</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Microsoft Corporation India Pvt. Ltd.</t>
+          <t>Citicorp Services India Pvt. Ltd. (CSIPL)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LOUIS MARESCA</t>
+          <t>SAURABH AGRAWAL</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-06-04 08:30:00</t>
+          <t>2026-06-04 05:45:00</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>9664988390</t>
+          <t>9552537476</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>swapnilraj@microsoft.com</t>
+          <t>saurabh1.agrawal@citi.com</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>E-Mandate</t>
+          <t>PG link</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-06-03 11:53:47.063000</t>
+          <t>2026-06-03 11:33:12.187000</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -909,27 +909,27 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Noida</t>
+          <t>Pune Hub 1</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>Outstation</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>SA56291</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>SA56291</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>SA56291</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
@@ -937,42 +937,42 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>WTI-20260603-3910477</t>
+          <t>WTI-20260603-3910536</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Self</t>
+          <t>Travel Desk</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Citicorp Services India Pvt. Ltd. (CSIPL)</t>
+          <t>Microsoft Corporation India Pvt. Ltd.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SWAPNIL SHROFF</t>
+          <t>LOUIS MARESCA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-06-04 09:00:00</t>
+          <t>2026-06-04 08:30:00</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>6261981321</t>
+          <t>9664988390</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>swapnil.shroff@citi.com</t>
+          <t>swapnilraj@microsoft.com</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>PG link</t>
+          <t>E-Mandate</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-06-03 10:58:28.053000</t>
+          <t>2026-06-03 11:53:47.063000</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>BLR Hub</t>
+          <t>Noida</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1002,17 +1002,17 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>ss38018</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>ss38018</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>ss38018</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
@@ -1020,7 +1020,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>WTI-20260603-3910479</t>
+          <t>WTI-20260603-3910477</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-06-04 17:30:00</t>
+          <t>2026-06-04 09:00:00</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-06-03 10:59:49.130000</t>
+          <t>2026-06-03 10:58:28.053000</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1103,42 +1103,42 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>WTI-20260603-3910478</t>
+          <t>WTI-20260603-3910578</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Self</t>
+          <t>Travel Desk</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Citicorp Services India Pvt. Ltd. (CSIPL)</t>
+          <t>Microsoft Corporation India Pvt. Ltd.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SWAPNIL SHROFF</t>
+          <t>ROHAN MISHRA</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-06-05 09:00:00</t>
+          <t>2026-06-04 12:15:00</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>6261981321</t>
+          <t>8097171155</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>swapnil.shroff@citi.com</t>
+          <t>Rohan.Mishra@microsoft.com</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>PG link</t>
+          <t>E-Mandate</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-06-03 10:58:56.477000</t>
+          <t>2026-06-03 12:22:24.650000</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1158,27 +1158,27 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>BLR Hub</t>
+          <t>Mumbai Hub</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>Outstation</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>ss38018</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>ss38018</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>ss38018</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>
@@ -1186,7 +1186,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>WTI-20260603-3910481</t>
+          <t>WTI-20260603-3910479</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-06-05 15:00:00</t>
+          <t>2026-06-04 17:30:00</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-06-03 11:02:09.430000</t>
+          <t>2026-06-03 10:59:49.130000</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Apt.Transfer / Office Drop</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1264,16 +1264,12 @@
           <t>ss38018</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>Fixed Transfer - Airport - 4 HRS 40 KMS Rate : 1595.00 ] PkgID:[287800]</t>
-        </is>
-      </c>
+      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>WTI-20260603-3910498</t>
+          <t>WTI-20260603-3910580</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1288,22 +1284,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ANAND JETHALIA</t>
+          <t>ROHAN MISHRA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-06-05 18:55:00</t>
+          <t>2026-06-05 07:00:00</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>9243701235</t>
+          <t>8097171155</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anand.Jethalia@microsoft.com</t>
+          <t>Rohan.Mishra@microsoft.com</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1318,7 +1314,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-06-03 11:25:17.133000</t>
+          <t>2026-06-03 12:23:49.903000</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1328,12 +1324,12 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>BLR Hub</t>
+          <t>Mumbai Hub</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>Apt.Transfer / Office Drop</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1351,12 +1347,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Airport - Transfer Rate : 1500.00 ] PkgID:[243643]</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>WTI-20260603-3910483</t>
+          <t>WTI-20260603-3910478</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-06-05 22:15:00</t>
+          <t>2026-06-05 09:00:00</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-06-03 11:03:38.450000</t>
+          <t>2026-06-03 10:58:56.477000</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1411,12 +1411,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Pune Hub 1</t>
+          <t>BLR Hub</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Apt.Transfer / Office Drop</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1434,98 +1434,936 @@
           <t>ss38018</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>Fixed Transfer - Airport - 4 HRS 40 KMS Rate : 1595.00 ] PkgID:[287862]</t>
-        </is>
-      </c>
+      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>WTI-20260603-3910582</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Travel Desk</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation India Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ROHAN MISHRA</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026-06-05 10:00:00</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>8097171155</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Rohan.Mishra@microsoft.com</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>E-Mandate</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Yudhveer Singh W04209</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>2026-06-03 12:26:12.570000</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>New Booking</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Gurugram</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>WTI-20260603-3910481</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Citicorp Services India Pvt. Ltd. (CSIPL)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>SWAPNIL SHROFF</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2026-06-05 15:00:00</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>6261981321</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>swapnil.shroff@citi.com</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>PG link</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Yudhveer Singh W04209</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:02:09.430000</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>New Booking</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>BLR Hub</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Apt.Transfer / Office Drop</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>ss38018</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>ss38018</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>ss38018</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Fixed Transfer - Airport - 4 HRS 40 KMS Rate : 1595.00 ] PkgID:[287800]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>WTI-20260603-3910498</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Travel Desk</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation India Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>ANAND JETHALIA</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2026-06-05 18:55:00</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>9243701235</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Anand.Jethalia@microsoft.com</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>E-Mandate</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Yudhveer Singh W04209</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:25:17.133000</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>New Booking</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>BLR Hub</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>WTI-20260603-3910586</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Travel Desk</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation India Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ROHAN MISHRA</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2026-06-05 19:15:00</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>8097171155</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Rohan.Mishra@microsoft.com</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>E-Mandate</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Yudhveer Singh W04209</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2026-06-03 12:27:54.993000</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>New Booking</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Mumbai Hub</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>WTI-20260603-3910483</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Citicorp Services India Pvt. Ltd. (CSIPL)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>SWAPNIL SHROFF</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2026-06-05 22:15:00</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>6261981321</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>swapnil.shroff@citi.com</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>PG link</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Yudhveer Singh W04209</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2026-06-03 11:03:38.450000</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>New Booking</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Pune Hub 1</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Apt.Transfer / Office Drop</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>ss38018</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>ss38018</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>ss38018</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Fixed Transfer - Airport - 4 HRS 40 KMS Rate : 1595.00 ] PkgID:[287862]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>WTI-20260603-3910520</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Travel Desk</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Microsoft Corporation India Pvt. Ltd.</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>MR. SOWMY SRINIVASAN</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>2026-06-21 19:20:00</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>9810369829</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>surabhiraman@microsoft.com</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>E-Mandate</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>Yudhveer Singh W04209</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>2026-06-03 11:46:29.187000</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>New Booking</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>Gurugram</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>Apt.Transfer / Office Drop</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
         <is>
           <t>Airport Transfer Rate : 2500.00 ] PkgID:[243329]</t>
         </is>
       </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>WTI-20260603-3910544</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Travel Desk</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation India Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>MR. SOWMY SRINIVASAN</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2026-06-22 07:00:00</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>9810369829</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>surabhiraman@microsoft.com</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>E-Mandate</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Naveen S</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>2026-06-03 12:02:52.993000</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>New Booking</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Gurugram</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>WTI-20260603-3910547</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Travel Desk</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation India Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>MR. SOWMY SRINIVASAN</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2026-06-23 07:00:00</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>9810369829</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>surabhiraman@microsoft.com</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>E-Mandate</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Yudhveer Singh W04209</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2026-06-03 12:04:00.817000</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>New Booking</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Gurugram</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>WTI-20260603-3910548</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Travel Desk</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation India Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>MR. SOWMY SRINIVASAN</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2026-06-24 07:00:00</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>9810369829</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>surabhiraman@microsoft.com</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>E-Mandate</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Yudhveer Singh W04209</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>2026-06-03 12:05:53.753000</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>New Booking</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Gurugram</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>WTI-20260603-3910552</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Travel Desk</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation India Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>MR. SOWMY SRINIVASAN</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2026-06-24 21:50:00</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>9810369829</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>surabhiraman@microsoft.com</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>E-Mandate</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Yudhveer Singh W04209</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2026-06-03 12:07:12.980000</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>New Booking</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Hyderabad Hub</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Apt.Transfer / Office Drop</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Airport - Transfer Rate : 2500.00 ] PkgID:[243641]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>WTI-20260603-3910555</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Travel Desk</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation India Pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>MR. SOWMY SRINIVASAN</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2026-06-25 07:00:00</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>9810369829</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>surabhiraman@microsoft.com</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>E-Mandate</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Yudhveer Singh W04209</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>2026-06-03 12:10:25.820000</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>New Booking</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Hyderabad Hub</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
